--- a/grupo-aplic.xlsx
+++ b/grupo-aplic.xlsx
@@ -1,110 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gustavo.souza\Desktop\Projeto-extrato\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="2"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="600" firstSheet="0" activeTab="2" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Bradesco" sheetId="1" r:id="rId1"/>
-    <sheet name="Santander" sheetId="2" r:id="rId2"/>
-    <sheet name="Itau" sheetId="3" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bradesco" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Santander" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Itau" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="152511" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
-  <si>
-    <t>Grupo</t>
-  </si>
-  <si>
-    <t>Descrição</t>
-  </si>
-  <si>
-    <t>INVEST FACIL</t>
-  </si>
-  <si>
-    <t>RENTAB.INVEST FACILCRED*</t>
-  </si>
-  <si>
-    <t>CDB</t>
-  </si>
-  <si>
-    <t>Contamax</t>
-  </si>
-  <si>
-    <t>contamax</t>
-  </si>
-  <si>
-    <t>oper compromissada</t>
-  </si>
-  <si>
-    <t>OPER COMPROMISSADA</t>
-  </si>
-  <si>
-    <t>premium di</t>
-  </si>
-  <si>
-    <t>PREMIUM DI</t>
-  </si>
-  <si>
-    <t>premium rf</t>
-  </si>
-  <si>
-    <t>PREMIUM RF</t>
-  </si>
-  <si>
-    <t>aplic</t>
-  </si>
-  <si>
-    <t>APLIC AUTOMATICO</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="1">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -126,16 +64,16 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
+        <color theme="0" tint="-0.1499679555650502"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
+        <color theme="0" tint="-0.1499679555650502"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
+        <color theme="0" tint="-0.1499679555650502"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.14996795556505021"/>
+        <color theme="0" tint="-0.1499679555650502"/>
       </bottom>
       <diagonal/>
     </border>
@@ -165,40 +103,99 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma 2" xfId="2"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1"/>
+    <cellStyle name="Comma 2" xfId="2"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:B9" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:B9" headerRowCount="1" totalsRowShown="0">
   <autoFilter ref="A1:B9"/>
   <tableColumns count="2">
     <tableColumn id="1" name="Descrição"/>
@@ -470,162 +467,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="34.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col width="34.42578125" customWidth="1" min="1" max="1"/>
+    <col width="24.7109375" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>RENTAB.INVEST FACILCRED*</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>INVEST FACIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Contamax</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>contamax</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.140625" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="7"/>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Descrição</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>oper compromissada</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPER COMPROMISSADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>premium di</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PREMIUM DI</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>premium rf</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PREMIUM RF</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>APLIC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>APLICAÇÂO AUTOMATICA</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/grupo-aplic.xlsx
+++ b/grupo-aplic.xlsx
@@ -579,7 +579,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -645,12 +645,24 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>APLIC</t>
+          <t>APLIC AUT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>APLICAÇÂO AUTOMATICA</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PRIVILEGE</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PRIVILEGE</t>
         </is>
       </c>
     </row>
